--- a/lista-debitare-dulap-hol.xlsx
+++ b/lista-debitare-dulap-hol.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -451,7 +451,8 @@
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="40" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="48" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -512,6 +513,11 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>Notă</t>
         </is>
       </c>
@@ -553,6 +559,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
+          <t>PAL corp</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
           <t>L1 = muchia din față, l2 = muchia de jos</t>
         </is>
       </c>
@@ -591,6 +602,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
+          <t>PAL corp</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
           <t>l1 = muchia din față</t>
         </is>
       </c>
@@ -629,6 +645,11 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
+          <t>PAL corp</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
           <t>l1 = muchia din față</t>
         </is>
       </c>
@@ -667,6 +688,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
+          <t>PAL fronturi</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
           <t>L1 = muchia de jos</t>
         </is>
       </c>
@@ -714,6 +740,11 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
+          <t>PAL fronturi</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
           <t>4 muchii</t>
         </is>
       </c>
@@ -755,6 +786,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
+          <t>PAL corp</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
           <t>L1 = muchia din față, l2 = muchia de jos</t>
         </is>
       </c>
@@ -793,6 +829,11 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
+          <t>PAL corp</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
           <t>l1 = muchia din față</t>
         </is>
       </c>
@@ -831,6 +872,11 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
+          <t>PAL corp</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
           <t>L1 = muchia din față</t>
         </is>
       </c>
@@ -869,6 +915,11 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
+          <t>PAL fronturi</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
           <t>L1 = muchia de jos</t>
         </is>
       </c>
@@ -916,6 +967,11 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
+          <t>PAL fronturi</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
           <t>4 muchii</t>
         </is>
       </c>
@@ -940,7 +996,7 @@
         <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>460</v>
+        <v>420</v>
       </c>
       <c r="F12" t="n">
         <v>480</v>
@@ -948,9 +1004,6 @@
       <c r="G12" t="n">
         <v>0.8</v>
       </c>
-      <c r="I12" t="n">
-        <v>0.8</v>
-      </c>
       <c r="J12" t="n">
         <v>0.8</v>
       </c>
@@ -960,7 +1013,12 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>L1 = față, l1 = sus, l2 = jos</t>
+          <t>PAL corp</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>L1 = față, l2 = jos (sus e acoperit de placa pernei)</t>
         </is>
       </c>
     </row>
@@ -990,7 +1048,7 @@
         <v>464</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="K13" s="2">
         <f>D13*E13*F13/1000000</f>
@@ -998,6 +1056,11 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
+          <t>PAL corp</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
           <t>l1 = muchia din față</t>
         </is>
       </c>
@@ -1036,6 +1099,11 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
+          <t>PAL corp</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
           <t>l1 = muchia din față</t>
         </is>
       </c>
@@ -1074,6 +1142,11 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
+          <t>PAL fronturi</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
           <t>L1 = muchia de jos</t>
         </is>
       </c>
@@ -1101,7 +1174,7 @@
         <v>496</v>
       </c>
       <c r="F16" t="n">
-        <v>378</v>
+        <v>356</v>
       </c>
       <c r="G16" t="n">
         <v>2</v>
@@ -1121,6 +1194,11 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
+          <t>PAL fronturi</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
           <t>4 muchii</t>
         </is>
       </c>
@@ -1128,39 +1206,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3P-PAN</t>
+          <t>3B-PERNA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Corp 3 · Panou cuier</t>
+          <t>Corp 3 · Bancă</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Panou perete</t>
+          <t>Placă pernă (burete 20 + catifea)</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>1300</v>
+        <v>500</v>
       </c>
       <c r="F17" t="n">
-        <v>500</v>
-      </c>
-      <c r="G17" t="n">
-        <v>2</v>
-      </c>
-      <c r="H17" t="n">
-        <v>2</v>
-      </c>
-      <c r="I17" t="n">
-        <v>2</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2</v>
+        <v>480</v>
       </c>
       <c r="K17" s="2">
         <f>D17*E17*F17/1000000</f>
@@ -1168,40 +1234,39 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>4 muchii</t>
+          <t>PAL fronturi</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>fără cant; se prinde cu șuruburi din interior</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3S-LAT</t>
+          <t>3P-PAN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Corp 3 · Suspendat</t>
+          <t>Corp 3 · Panou cuier</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Laterală</t>
+          <t>Panou perete (burete + catifea)</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>600</v>
+        <v>1340</v>
       </c>
       <c r="F18" t="n">
-        <v>480</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.8</v>
+        <v>500</v>
       </c>
       <c r="K18" s="2">
         <f>D18*E18*F18/1000000</f>
@@ -1209,14 +1274,19 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>L1 = față, l2 = jos</t>
+          <t>PAL fronturi</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>fără cant; se îmbracă în burete 20 + catifea</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3S-CAP</t>
+          <t>3S-LAT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1226,19 +1296,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Capac / fund</t>
+          <t>Laterală</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>2</v>
       </c>
       <c r="E19" t="n">
+        <v>600</v>
+      </c>
+      <c r="F19" t="n">
         <v>480</v>
       </c>
-      <c r="F19" t="n">
-        <v>464</v>
-      </c>
-      <c r="I19" t="n">
+      <c r="G19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J19" t="n">
         <v>0.8</v>
       </c>
       <c r="K19" s="2">
@@ -1247,14 +1320,19 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>l1 = muchia din față</t>
+          <t>PAL corp</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>L1 = față, l2 = jos</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3S-USA</t>
+          <t>3S-CAP</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1264,29 +1342,20 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ușă</t>
+          <t>Capac / fund</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
-        <v>596</v>
+        <v>480</v>
       </c>
       <c r="F20" t="n">
-        <v>496</v>
-      </c>
-      <c r="G20" t="n">
-        <v>2</v>
-      </c>
-      <c r="H20" t="n">
-        <v>2</v>
+        <v>464</v>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="K20" s="2">
         <f>D20*E20*F20/1000000</f>
@@ -1294,29 +1363,151 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
+          <t>PAL corp</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>l1 = muchia din față</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>3S-POL</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Corp 3 · Suspendat</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Poliță mobilă</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>462</v>
+      </c>
+      <c r="F21" t="n">
+        <v>440</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K21" s="2">
+        <f>D21*E21*F21/1000000</f>
+        <v/>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>PAL fronturi</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>L1 = muchia din față; material fronturi</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>3S-USA</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Corp 3 · Suspendat</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ușă</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>596</v>
+      </c>
+      <c r="F22" t="n">
+        <v>496</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2</v>
+      </c>
+      <c r="K22" s="2">
+        <f>D22*E22*F22/1000000</f>
+        <v/>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>PAL fronturi</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
           <t>4 muchii</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="C21" s="3" t="inlineStr">
+    <row r="23">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="D21">
-        <f>SUM(D2:D20)</f>
-        <v/>
-      </c>
-      <c r="K21" s="2">
-        <f>SUM(K2:K20)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Cote finite (după cant). Muchii: L = laturile lungi, l = cele scurte; valoarea e grosimea cantului în mm.</t>
+      <c r="D23">
+        <f>SUM(D2:D22)</f>
+        <v/>
+      </c>
+      <c r="K23" s="2">
+        <f>SUM(K2:K22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Din care PAL corp</t>
+        </is>
+      </c>
+      <c r="K24" s="2">
+        <f>SUMIF(L2:L22,"PAL corp",K2:K22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Din care PAL fronturi</t>
+        </is>
+      </c>
+      <c r="K25" s="2">
+        <f>SUMIF(L2:L22,"PAL fronturi",K2:K22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Panoul de cuier și placa pernei: fără cant (se îmbracă în burete 20 mm + catifea). Cote finite (după cant). Muchii: L = laturile lungi, l = cele scurte; valoarea e grosimea cantului în mm.</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1605,7 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>456</v>
+        <v>416</v>
       </c>
       <c r="E3" t="n">
         <v>496</v>
@@ -1512,7 +1703,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>25.622</v>
+        <v>25.508</v>
       </c>
       <c r="C2" s="4">
         <f>B2*1.1</f>
@@ -1524,7 +1715,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>19.164</v>
+        <v>15.056</v>
       </c>
       <c r="C3" s="4">
         <f>B3*1.1</f>
@@ -1542,7 +1733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -1604,86 +1795,152 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>8 polițe mobile × 4 + rezervă; de verificat tipul</t>
+          <t>8 polițe mobile × 4 (corp 2) + 4 (suspendat) + 4 rezervă; de verificat tipul</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Bară umerașe Ø25 cu suporți</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2</v>
+          <t>Burete 20 mm</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0,9 m²</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>corp 1, poziții orientative</t>
+          <t>panou 1340 × 500 și pernă 500 × 480; cu rezervă</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Colțare metalice pentru perete</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>10</v>
+          <t>Catifea</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>~2 m²</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4 pe corp înalt, 2 pe bancă</t>
+          <t>se înfășoară peste muchii</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Suporți de suspendare pentru corpul suspendat</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2</v>
+          <t>Capsator de tapițerie + adeziv</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>după fișa suportului</t>
+          <t>pentru panou și pernă</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cârlige panou cuier</t>
+          <t>Șuruburi scurte pentru placa pernei</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>poziții orientative</t>
+          <t>max. 30 mm de la fața de jos a șezutului</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Bară umerașe Ø25 cu suporți</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>corp 1, poziții orientative</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Colțare metalice pentru perete</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>10</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>4 pe corp înalt, 2 pe bancă</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Suporți de suspendare pentru corpul suspendat</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>după fișa suportului</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Cârlige panou cuier</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>poziții orientative</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>Șuruburi, dibluri, șuruburi de asamblare</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>alege utilizatorul, în funcție de perete</t>
         </is>
